--- a/VerveStacks_USA/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_USA/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_USA\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B23B0E89-0A5C-416B-9702-88A134B1FE34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EB48FAE1-2F7E-4731-BE43-E6A69989F0DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,6 +40,32 @@
     <author>Amit Kanudia</author>
   </authors>
   <commentList>
+    <comment ref="B5" authorId="0" shapeId="0" xr:uid="{2FF9EF2B-EBD7-4C7E-9F26-8FF1228838F5}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Amit Kanudia:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+11-09-2025
+AFS will be sufficient
+</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="D8" authorId="0" shapeId="0" xr:uid="{79577DE7-359E-49C1-A1D9-EC64BAD436CB}">
       <text>
         <r>
@@ -97,7 +123,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1536" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1536" uniqueCount="94">
   <si>
     <t>~TFM_INS-AT</t>
   </si>
@@ -294,9 +320,6 @@
     <t>UCE_max nuclear capacity</t>
   </si>
   <si>
-    <t>UC_RHSRT~2050</t>
-  </si>
-  <si>
     <t>life</t>
   </si>
   <si>
@@ -360,6 +383,15 @@
     <t>wind*</t>
   </si>
   <si>
+    <t>~UC_T: 2050</t>
+  </si>
+  <si>
+    <t>base-year nuclear capacity</t>
+  </si>
+  <si>
+    <t>\I: hydro</t>
+  </si>
+  <si>
     <t>geothermal</t>
   </si>
   <si>
@@ -382,7 +414,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -432,8 +464,24 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -450,6 +498,11 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -480,13 +533,14 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -497,10 +551,13 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="4"/>
   </cellXfs>
-  <cellStyles count="4">
+  <cellStyles count="5">
     <cellStyle name="Heading 3" xfId="2" builtinId="18"/>
     <cellStyle name="Heading 4" xfId="3" builtinId="19"/>
+    <cellStyle name="Neutral" xfId="4" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
@@ -947,15 +1004,12 @@
     </row>
     <row r="5" spans="1:38" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
-        <v>6</v>
+        <v>88</v>
       </c>
       <c r="C5" t="s">
         <v>43</v>
       </c>
-      <c r="D5" s="4">
-        <f>IFERROR(VLOOKUP(B5,$F$3:$J$11,5,FALSE),"")</f>
-        <v>0.3892785813467925</v>
-      </c>
+      <c r="D5" s="4"/>
       <c r="F5" t="s">
         <v>8</v>
       </c>
@@ -977,7 +1031,7 @@
         <v>0.28000000000000003</v>
       </c>
       <c r="B6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C6" t="s">
         <v>7</v>
@@ -987,7 +1041,7 @@
         <v/>
       </c>
       <c r="F6" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
@@ -1006,7 +1060,7 @@
     </row>
     <row r="7" spans="1:38" x14ac:dyDescent="0.45">
       <c r="B7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C7" t="s">
         <v>7</v>
@@ -1244,7 +1298,7 @@
     </row>
     <row r="11" spans="1:38" ht="14.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="F11" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
@@ -1257,7 +1311,7 @@
     </row>
     <row r="12" spans="1:38" x14ac:dyDescent="0.45">
       <c r="F12" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G12" s="3">
         <v>0.19932808100882485</v>
@@ -1277,7 +1331,7 @@
         <v>26</v>
       </c>
       <c r="U13" t="s">
-        <v>10</v>
+        <v>86</v>
       </c>
     </row>
     <row r="14" spans="1:38" x14ac:dyDescent="0.45">
@@ -1317,9 +1371,6 @@
       <c r="AC14" t="s">
         <v>17</v>
       </c>
-      <c r="AD14" t="s">
-        <v>65</v>
-      </c>
     </row>
     <row r="15" spans="1:38" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
@@ -1333,7 +1384,7 @@
         <v>Hydropower - large-scale unit,Solar photovoltaics - Large scale unit,Wind offshore,Wind onshore</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="U15" t="s">
         <v>64</v>
@@ -1345,15 +1396,18 @@
         <v>1</v>
       </c>
       <c r="AB15">
+        <f>AE15*2.5</f>
+        <v>236.64999999999998</v>
+      </c>
+      <c r="AC15">
+        <v>3</v>
+      </c>
+      <c r="AE15" s="11">
         <f>SUMIFS(historical_data_long!$D$3:$D$626,historical_data_long!$A$3:$A$626,Veda!$V15,historical_data_long!$C$3:$C$626,"GW",historical_data_long!$B$3:$B$626,2022)</f>
         <v>94.66</v>
       </c>
-      <c r="AC15">
-        <v>3</v>
-      </c>
-      <c r="AD15">
-        <f>AB15*2.5</f>
-        <v>236.64999999999998</v>
+      <c r="AF15" s="10" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="16" spans="1:38" x14ac:dyDescent="0.45">
@@ -1495,24 +1549,24 @@
     </row>
     <row r="28" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B28" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E28">
         <v>50</v>
       </c>
       <c r="G28" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="29" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B29" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E29">
         <v>8.76</v>
       </c>
       <c r="G29" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.45">
@@ -1575,7 +1629,7 @@
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.45">
       <c r="D40" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E40">
         <v>-1</v>
@@ -1583,7 +1637,8 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -1606,41 +1661,41 @@
   <sheetData>
     <row r="9" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C10" t="s">
+        <v>69</v>
+      </c>
+      <c r="D10" t="s">
         <v>70</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>71</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>72</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>73</v>
       </c>
-      <c r="G10" t="s">
+      <c r="H10" t="s">
         <v>74</v>
       </c>
-      <c r="H10" t="s">
+      <c r="I10" t="s">
         <v>75</v>
       </c>
-      <c r="I10" t="s">
+      <c r="J10" t="s">
         <v>76</v>
-      </c>
-      <c r="J10" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C11">
         <v>25</v>
@@ -1674,7 +1729,7 @@
     </row>
     <row r="18" spans="1:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B18" s="9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
@@ -1682,16 +1737,16 @@
         <v>48</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C19" s="8" t="s">
         <v>2</v>
       </c>
       <c r="D19" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="E19" s="8" t="s">
         <v>80</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>81</v>
       </c>
       <c r="F19" s="8">
         <v>2025</v>
@@ -1716,7 +1771,7 @@
         <v>solar</v>
       </c>
       <c r="D20" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E20">
         <v>1</v>
@@ -1746,7 +1801,7 @@
         <v>wind*</v>
       </c>
       <c r="D21" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E21">
         <v>1</v>
@@ -1776,7 +1831,7 @@
         <v>hydro</v>
       </c>
       <c r="D22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E22">
         <v>1</v>
@@ -1806,7 +1861,7 @@
         <v>nuclear</v>
       </c>
       <c r="D23" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E23">
         <v>1</v>
@@ -1961,7 +2016,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B10">
         <v>2000</v>
@@ -2087,7 +2142,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B19">
         <v>2001</v>
@@ -2213,7 +2268,7 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B28">
         <v>2002</v>
@@ -2339,7 +2394,7 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B37">
         <v>2003</v>
@@ -2465,7 +2520,7 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B46">
         <v>2004</v>
@@ -2591,7 +2646,7 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B55">
         <v>2005</v>
@@ -2717,7 +2772,7 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B64">
         <v>2006</v>
@@ -2843,7 +2898,7 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B73">
         <v>2007</v>
@@ -2969,7 +3024,7 @@
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B82">
         <v>2008</v>
@@ -3095,7 +3150,7 @@
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A91" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B91">
         <v>2009</v>
@@ -3221,7 +3276,7 @@
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A100" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B100">
         <v>2010</v>
@@ -3347,7 +3402,7 @@
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A109" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B109">
         <v>2011</v>
@@ -3473,7 +3528,7 @@
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A118" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B118">
         <v>2012</v>
@@ -3599,7 +3654,7 @@
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A127" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B127">
         <v>2013</v>
@@ -3725,7 +3780,7 @@
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A136" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B136">
         <v>2014</v>
@@ -3851,7 +3906,7 @@
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A145" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B145">
         <v>2015</v>
@@ -3977,7 +4032,7 @@
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A154" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B154">
         <v>2016</v>
@@ -4103,7 +4158,7 @@
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A163" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B163">
         <v>2017</v>
@@ -4229,7 +4284,7 @@
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A172" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B172">
         <v>2018</v>
@@ -4355,7 +4410,7 @@
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A181" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B181">
         <v>2019</v>
@@ -4481,7 +4536,7 @@
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A190" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B190">
         <v>2020</v>
@@ -4607,7 +4662,7 @@
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A199" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B199">
         <v>2021</v>
@@ -4733,7 +4788,7 @@
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A208" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B208">
         <v>2022</v>
@@ -4859,7 +4914,7 @@
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A217" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B217">
         <v>2023</v>
@@ -4985,7 +5040,7 @@
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A226" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B226">
         <v>2000</v>
@@ -5111,7 +5166,7 @@
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A235" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B235">
         <v>2001</v>
@@ -5237,7 +5292,7 @@
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A244" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B244">
         <v>2002</v>
@@ -5363,7 +5418,7 @@
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A253" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B253">
         <v>2003</v>
@@ -5489,7 +5544,7 @@
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A262" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B262">
         <v>2004</v>
@@ -5615,7 +5670,7 @@
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A271" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B271">
         <v>2005</v>
@@ -5741,7 +5796,7 @@
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A280" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B280">
         <v>2006</v>
@@ -5867,7 +5922,7 @@
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A289" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B289">
         <v>2007</v>
@@ -5993,7 +6048,7 @@
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A298" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B298">
         <v>2008</v>
@@ -6119,7 +6174,7 @@
     </row>
     <row r="307" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A307" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B307">
         <v>2009</v>
@@ -6245,7 +6300,7 @@
     </row>
     <row r="316" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A316" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B316">
         <v>2010</v>
@@ -6371,7 +6426,7 @@
     </row>
     <row r="325" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A325" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B325">
         <v>2011</v>
@@ -6497,7 +6552,7 @@
     </row>
     <row r="334" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A334" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B334">
         <v>2012</v>
@@ -6623,7 +6678,7 @@
     </row>
     <row r="343" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A343" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B343">
         <v>2013</v>
@@ -6749,7 +6804,7 @@
     </row>
     <row r="352" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A352" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B352">
         <v>2014</v>
@@ -6875,7 +6930,7 @@
     </row>
     <row r="361" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A361" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B361">
         <v>2015</v>
@@ -7001,7 +7056,7 @@
     </row>
     <row r="370" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A370" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B370">
         <v>2016</v>
@@ -7127,7 +7182,7 @@
     </row>
     <row r="379" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A379" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B379">
         <v>2017</v>
@@ -7253,7 +7308,7 @@
     </row>
     <row r="388" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A388" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B388">
         <v>2018</v>
@@ -7379,7 +7434,7 @@
     </row>
     <row r="397" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A397" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B397">
         <v>2019</v>
@@ -7505,7 +7560,7 @@
     </row>
     <row r="406" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A406" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B406">
         <v>2020</v>
@@ -7631,7 +7686,7 @@
     </row>
     <row r="415" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A415" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B415">
         <v>2021</v>
@@ -7757,7 +7812,7 @@
     </row>
     <row r="424" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A424" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B424">
         <v>2022</v>
@@ -7883,7 +7938,7 @@
     </row>
     <row r="433" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A433" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B433">
         <v>2023</v>
@@ -8009,7 +8064,7 @@
     </row>
     <row r="442" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A442" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B442">
         <v>2000</v>
@@ -8135,7 +8190,7 @@
     </row>
     <row r="451" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A451" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B451">
         <v>2001</v>
@@ -8261,7 +8316,7 @@
     </row>
     <row r="460" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A460" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B460">
         <v>2002</v>
@@ -8387,7 +8442,7 @@
     </row>
     <row r="469" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A469" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B469">
         <v>2003</v>
@@ -8513,7 +8568,7 @@
     </row>
     <row r="478" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A478" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B478">
         <v>2004</v>
@@ -8639,7 +8694,7 @@
     </row>
     <row r="487" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A487" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B487">
         <v>2005</v>
@@ -8765,7 +8820,7 @@
     </row>
     <row r="496" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A496" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B496">
         <v>2006</v>
@@ -8891,7 +8946,7 @@
     </row>
     <row r="505" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A505" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B505">
         <v>2007</v>
@@ -9017,7 +9072,7 @@
     </row>
     <row r="514" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A514" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B514">
         <v>2008</v>
@@ -9143,7 +9198,7 @@
     </row>
     <row r="523" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A523" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B523">
         <v>2009</v>
@@ -9269,7 +9324,7 @@
     </row>
     <row r="532" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A532" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B532">
         <v>2010</v>
@@ -9395,7 +9450,7 @@
     </row>
     <row r="541" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A541" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B541">
         <v>2011</v>
@@ -9521,7 +9576,7 @@
     </row>
     <row r="550" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A550" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B550">
         <v>2012</v>
@@ -9647,7 +9702,7 @@
     </row>
     <row r="559" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A559" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B559">
         <v>2013</v>
@@ -9773,7 +9828,7 @@
     </row>
     <row r="568" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A568" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B568">
         <v>2014</v>
@@ -9899,7 +9954,7 @@
     </row>
     <row r="577" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A577" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B577">
         <v>2015</v>
@@ -10025,7 +10080,7 @@
     </row>
     <row r="586" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A586" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B586">
         <v>2016</v>
@@ -10151,7 +10206,7 @@
     </row>
     <row r="595" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A595" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B595">
         <v>2017</v>
@@ -10277,7 +10332,7 @@
     </row>
     <row r="604" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A604" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B604">
         <v>2018</v>
@@ -10403,7 +10458,7 @@
     </row>
     <row r="613" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A613" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B613">
         <v>2019</v>
@@ -10529,7 +10584,7 @@
     </row>
     <row r="622" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A622" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B622">
         <v>2020</v>
@@ -10655,7 +10710,7 @@
     </row>
     <row r="631" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A631" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B631">
         <v>2021</v>
@@ -10781,7 +10836,7 @@
     </row>
     <row r="640" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A640" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B640">
         <v>2022</v>
@@ -10907,7 +10962,7 @@
     </row>
     <row r="649" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A649" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B649">
         <v>2023</v>

--- a/VerveStacks_USA/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_USA/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_USA\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EB48FAE1-2F7E-4731-BE43-E6A69989F0DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{06DE6193-52F5-4A7E-B6C1-856CF82D8EB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -123,7 +123,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1536" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1556" uniqueCount="95">
   <si>
     <t>~TFM_INS-AT</t>
   </si>
@@ -390,6 +390,9 @@
   </si>
   <si>
     <t>\I: hydro</t>
+  </si>
+  <si>
+    <t>N/A</t>
   </si>
   <si>
     <t>geothermal</t>
@@ -957,11 +960,11 @@
       <c r="F3" t="s">
         <v>55</v>
       </c>
-      <c r="G3" s="3">
-        <v>0.54863047126229303</v>
-      </c>
-      <c r="H3" s="3">
-        <v>0.89062522319196646</v>
+      <c r="G3" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>89</v>
       </c>
       <c r="I3" s="3">
         <v>0.57869297792104235</v>
@@ -989,11 +992,11 @@
       <c r="F4" t="s">
         <v>5</v>
       </c>
-      <c r="G4" s="3">
-        <v>0.37884710642106634</v>
-      </c>
-      <c r="H4" s="3">
-        <v>0.68993375409691593</v>
+      <c r="G4" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>89</v>
       </c>
       <c r="I4" s="3">
         <v>0.45128471065076869</v>
@@ -1013,11 +1016,11 @@
       <c r="F5" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="3">
-        <v>0.23254337785044626</v>
-      </c>
-      <c r="H5" s="3">
-        <v>0.43459414324342821</v>
+      <c r="G5" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>89</v>
       </c>
       <c r="I5" s="3">
         <v>0.21452713874059057</v>
@@ -1041,10 +1044,14 @@
         <v/>
       </c>
       <c r="F6" t="s">
+        <v>90</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
+      <c r="H6" s="3" t="s">
+        <v>89</v>
+      </c>
       <c r="I6" s="3">
         <v>0.59758823019714979</v>
       </c>
@@ -1072,11 +1079,11 @@
       <c r="F7" t="s">
         <v>6</v>
       </c>
-      <c r="G7" s="3">
-        <v>0.30106784050434288</v>
-      </c>
-      <c r="H7" s="3">
-        <v>0.43326382946908459</v>
+      <c r="G7" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>89</v>
       </c>
       <c r="I7" s="3">
         <v>0.24865417698441153</v>
@@ -1140,18 +1147,18 @@
       <c r="C8" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="4" t="str">
         <f>IFERROR(VLOOKUP(B8,$F$3:$J$11,3,FALSE),"")</f>
-        <v>0.94168774792584609</v>
+        <v>N/A</v>
       </c>
       <c r="F8" t="s">
         <v>19</v>
       </c>
-      <c r="G8" s="3">
-        <v>0.86193992895014826</v>
-      </c>
-      <c r="H8" s="3">
-        <v>0.94168774792584609</v>
+      <c r="G8" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>89</v>
       </c>
       <c r="I8" s="3">
         <v>0.89761085725848577</v>
@@ -1172,13 +1179,13 @@
         <f>-1/8.76</f>
         <v>-0.11415525114155252</v>
       </c>
-      <c r="Z8" s="2">
+      <c r="Z8" s="2" t="str">
         <f>VLOOKUP(V8,$F$3:$J$11,3,FALSE)</f>
-        <v>0.68993375409691593</v>
-      </c>
-      <c r="AA8" s="2">
+        <v>N/A</v>
+      </c>
+      <c r="AA8" s="2" t="e">
         <f>Z8*$AB$1</f>
-        <v>0.75892712950660757</v>
+        <v>#VALUE!</v>
       </c>
       <c r="AB8">
         <v>0</v>
@@ -1196,13 +1203,13 @@
         <f>-1/8.76</f>
         <v>-0.11415525114155252</v>
       </c>
-      <c r="AI8" s="2">
+      <c r="AI8" s="2" t="str">
         <f>VLOOKUP(AG8,$F$3:$J$11,2,FALSE)</f>
-        <v>0.37884710642106634</v>
-      </c>
-      <c r="AJ8">
+        <v>N/A</v>
+      </c>
+      <c r="AJ8" t="e">
         <f>AI8*$AD$1</f>
-        <v>7.5769421284213267E-2</v>
+        <v>#VALUE!</v>
       </c>
       <c r="AK8">
         <v>0</v>
@@ -1215,11 +1222,11 @@
       <c r="F9" t="s">
         <v>23</v>
       </c>
-      <c r="G9" s="3">
-        <v>8.8500483037795494E-2</v>
-      </c>
-      <c r="H9" s="3">
-        <v>0.24242125602133488</v>
+      <c r="G9" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>89</v>
       </c>
       <c r="I9" s="3">
         <v>0.11213559179835184</v>
@@ -1240,13 +1247,13 @@
         <f>-1/8.76</f>
         <v>-0.11415525114155252</v>
       </c>
-      <c r="Z9" s="2">
+      <c r="Z9" s="2" t="str">
         <f>VLOOKUP(V9,$F$3:$J$11,3,FALSE)</f>
-        <v>0.43459414324342821</v>
-      </c>
-      <c r="AA9" s="2">
+        <v>N/A</v>
+      </c>
+      <c r="AA9" s="2" t="e">
         <f>Z9*$AB$1</f>
-        <v>0.47805355756777107</v>
+        <v>#VALUE!</v>
       </c>
       <c r="AB9">
         <v>0</v>
@@ -1264,13 +1271,13 @@
         <f>-1/8.76</f>
         <v>-0.11415525114155252</v>
       </c>
-      <c r="AI9" s="2">
+      <c r="AI9" s="2" t="str">
         <f>VLOOKUP(AG9,$F$3:$J$11,2,FALSE)</f>
-        <v>0.23254337785044626</v>
-      </c>
-      <c r="AJ9">
+        <v>N/A</v>
+      </c>
+      <c r="AJ9" t="e">
         <f>AI9*$AD$1</f>
-        <v>4.6508675570089253E-2</v>
+        <v>#VALUE!</v>
       </c>
       <c r="AK9">
         <v>0</v>
@@ -1283,11 +1290,11 @@
       <c r="F10" t="s">
         <v>9</v>
       </c>
-      <c r="G10" s="3">
-        <v>3.6837332815181839E-2</v>
-      </c>
-      <c r="H10" s="3">
-        <v>0.20499200320398811</v>
+      <c r="G10" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>89</v>
       </c>
       <c r="I10" s="3">
         <v>0.12571540459727984</v>
@@ -1298,10 +1305,14 @@
     </row>
     <row r="11" spans="1:38" ht="14.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="F11" t="s">
-        <v>90</v>
-      </c>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
+        <v>91</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>89</v>
+      </c>
       <c r="I11" s="3">
         <v>0.39999922078326866</v>
       </c>
@@ -1311,13 +1322,13 @@
     </row>
     <row r="12" spans="1:38" x14ac:dyDescent="0.45">
       <c r="F12" t="s">
-        <v>91</v>
-      </c>
-      <c r="G12" s="3">
-        <v>0.19932808100882485</v>
-      </c>
-      <c r="H12" s="3">
-        <v>0.34995147575899105</v>
+        <v>92</v>
+      </c>
+      <c r="G12" t="s">
+        <v>89</v>
+      </c>
+      <c r="H12" t="s">
+        <v>89</v>
       </c>
       <c r="I12" s="3">
         <v>0.20109032913765423</v>
@@ -1661,12 +1672,12 @@
   <sheetData>
     <row r="9" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C10" t="s">
         <v>69</v>
@@ -2016,7 +2027,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B10">
         <v>2000</v>
@@ -2142,7 +2153,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B19">
         <v>2001</v>
@@ -2268,7 +2279,7 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B28">
         <v>2002</v>
@@ -2394,7 +2405,7 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B37">
         <v>2003</v>
@@ -2520,7 +2531,7 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B46">
         <v>2004</v>
@@ -2646,7 +2657,7 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B55">
         <v>2005</v>
@@ -2772,7 +2783,7 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B64">
         <v>2006</v>
@@ -2898,7 +2909,7 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B73">
         <v>2007</v>
@@ -3024,7 +3035,7 @@
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B82">
         <v>2008</v>
@@ -3150,7 +3161,7 @@
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A91" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B91">
         <v>2009</v>
@@ -3276,7 +3287,7 @@
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A100" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B100">
         <v>2010</v>
@@ -3402,7 +3413,7 @@
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A109" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B109">
         <v>2011</v>
@@ -3528,7 +3539,7 @@
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A118" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B118">
         <v>2012</v>
@@ -3654,7 +3665,7 @@
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A127" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B127">
         <v>2013</v>
@@ -3780,7 +3791,7 @@
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A136" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B136">
         <v>2014</v>
@@ -3906,7 +3917,7 @@
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A145" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B145">
         <v>2015</v>
@@ -4032,7 +4043,7 @@
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A154" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B154">
         <v>2016</v>
@@ -4158,7 +4169,7 @@
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A163" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B163">
         <v>2017</v>
@@ -4284,7 +4295,7 @@
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A172" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B172">
         <v>2018</v>
@@ -4410,7 +4421,7 @@
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A181" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B181">
         <v>2019</v>
@@ -4536,7 +4547,7 @@
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A190" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B190">
         <v>2020</v>
@@ -4662,7 +4673,7 @@
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A199" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B199">
         <v>2021</v>
@@ -4788,7 +4799,7 @@
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A208" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B208">
         <v>2022</v>
@@ -4914,7 +4925,7 @@
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A217" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B217">
         <v>2023</v>
@@ -5040,7 +5051,7 @@
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A226" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B226">
         <v>2000</v>
@@ -5166,7 +5177,7 @@
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A235" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B235">
         <v>2001</v>
@@ -5292,7 +5303,7 @@
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A244" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B244">
         <v>2002</v>
@@ -5418,7 +5429,7 @@
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A253" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B253">
         <v>2003</v>
@@ -5544,7 +5555,7 @@
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A262" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B262">
         <v>2004</v>
@@ -5670,7 +5681,7 @@
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A271" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B271">
         <v>2005</v>
@@ -5796,7 +5807,7 @@
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A280" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B280">
         <v>2006</v>
@@ -5922,7 +5933,7 @@
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A289" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B289">
         <v>2007</v>
@@ -6048,7 +6059,7 @@
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A298" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B298">
         <v>2008</v>
@@ -6174,7 +6185,7 @@
     </row>
     <row r="307" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A307" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B307">
         <v>2009</v>
@@ -6300,7 +6311,7 @@
     </row>
     <row r="316" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A316" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B316">
         <v>2010</v>
@@ -6426,7 +6437,7 @@
     </row>
     <row r="325" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A325" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B325">
         <v>2011</v>
@@ -6552,7 +6563,7 @@
     </row>
     <row r="334" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A334" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B334">
         <v>2012</v>
@@ -6678,7 +6689,7 @@
     </row>
     <row r="343" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A343" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B343">
         <v>2013</v>
@@ -6804,7 +6815,7 @@
     </row>
     <row r="352" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A352" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B352">
         <v>2014</v>
@@ -6930,7 +6941,7 @@
     </row>
     <row r="361" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A361" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B361">
         <v>2015</v>
@@ -7056,7 +7067,7 @@
     </row>
     <row r="370" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A370" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B370">
         <v>2016</v>
@@ -7182,7 +7193,7 @@
     </row>
     <row r="379" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A379" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B379">
         <v>2017</v>
@@ -7308,7 +7319,7 @@
     </row>
     <row r="388" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A388" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B388">
         <v>2018</v>
@@ -7434,7 +7445,7 @@
     </row>
     <row r="397" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A397" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B397">
         <v>2019</v>
@@ -7560,7 +7571,7 @@
     </row>
     <row r="406" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A406" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B406">
         <v>2020</v>
@@ -7686,7 +7697,7 @@
     </row>
     <row r="415" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A415" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B415">
         <v>2021</v>
@@ -7812,7 +7823,7 @@
     </row>
     <row r="424" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A424" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B424">
         <v>2022</v>
@@ -7938,7 +7949,7 @@
     </row>
     <row r="433" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A433" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B433">
         <v>2023</v>
@@ -8064,7 +8075,7 @@
     </row>
     <row r="442" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A442" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B442">
         <v>2000</v>
@@ -8190,7 +8201,7 @@
     </row>
     <row r="451" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A451" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B451">
         <v>2001</v>
@@ -8316,7 +8327,7 @@
     </row>
     <row r="460" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A460" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B460">
         <v>2002</v>
@@ -8442,7 +8453,7 @@
     </row>
     <row r="469" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A469" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B469">
         <v>2003</v>
@@ -8568,7 +8579,7 @@
     </row>
     <row r="478" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A478" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B478">
         <v>2004</v>
@@ -8694,7 +8705,7 @@
     </row>
     <row r="487" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A487" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B487">
         <v>2005</v>
@@ -8820,7 +8831,7 @@
     </row>
     <row r="496" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A496" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B496">
         <v>2006</v>
@@ -8946,7 +8957,7 @@
     </row>
     <row r="505" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A505" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B505">
         <v>2007</v>
@@ -9072,7 +9083,7 @@
     </row>
     <row r="514" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A514" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B514">
         <v>2008</v>
@@ -9198,7 +9209,7 @@
     </row>
     <row r="523" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A523" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B523">
         <v>2009</v>
@@ -9324,7 +9335,7 @@
     </row>
     <row r="532" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A532" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B532">
         <v>2010</v>
@@ -9450,7 +9461,7 @@
     </row>
     <row r="541" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A541" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B541">
         <v>2011</v>
@@ -9576,7 +9587,7 @@
     </row>
     <row r="550" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A550" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B550">
         <v>2012</v>
@@ -9702,7 +9713,7 @@
     </row>
     <row r="559" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A559" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B559">
         <v>2013</v>
@@ -9828,7 +9839,7 @@
     </row>
     <row r="568" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A568" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B568">
         <v>2014</v>
@@ -9954,7 +9965,7 @@
     </row>
     <row r="577" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A577" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B577">
         <v>2015</v>
@@ -10080,7 +10091,7 @@
     </row>
     <row r="586" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A586" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B586">
         <v>2016</v>
@@ -10206,7 +10217,7 @@
     </row>
     <row r="595" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A595" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B595">
         <v>2017</v>
@@ -10332,7 +10343,7 @@
     </row>
     <row r="604" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A604" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B604">
         <v>2018</v>
@@ -10458,7 +10469,7 @@
     </row>
     <row r="613" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A613" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B613">
         <v>2019</v>
@@ -10584,7 +10595,7 @@
     </row>
     <row r="622" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A622" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B622">
         <v>2020</v>
@@ -10710,7 +10721,7 @@
     </row>
     <row r="631" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A631" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B631">
         <v>2021</v>
@@ -10836,7 +10847,7 @@
     </row>
     <row r="640" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A640" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B640">
         <v>2022</v>
@@ -10962,7 +10973,7 @@
     </row>
     <row r="649" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A649" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B649">
         <v>2023</v>

--- a/VerveStacks_USA/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_USA/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_USA\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{06DE6193-52F5-4A7E-B6C1-856CF82D8EB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9D3E65E1-4A1A-4410-99D2-42D8698516C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -123,7 +123,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1556" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1536" uniqueCount="94">
   <si>
     <t>~TFM_INS-AT</t>
   </si>
@@ -390,9 +390,6 @@
   </si>
   <si>
     <t>\I: hydro</t>
-  </si>
-  <si>
-    <t>N/A</t>
   </si>
   <si>
     <t>geothermal</t>
@@ -960,11 +957,11 @@
       <c r="F3" t="s">
         <v>55</v>
       </c>
-      <c r="G3" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>89</v>
+      <c r="G3" s="3">
+        <v>0.54863047126229303</v>
+      </c>
+      <c r="H3" s="3">
+        <v>0.89062522319196646</v>
       </c>
       <c r="I3" s="3">
         <v>0.57869297792104235</v>
@@ -992,11 +989,11 @@
       <c r="F4" t="s">
         <v>5</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>89</v>
+      <c r="G4" s="3">
+        <v>0.37884710642106634</v>
+      </c>
+      <c r="H4" s="3">
+        <v>0.68993375409691593</v>
       </c>
       <c r="I4" s="3">
         <v>0.45128471065076869</v>
@@ -1016,11 +1013,11 @@
       <c r="F5" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>89</v>
+      <c r="G5" s="3">
+        <v>0.23254337785044626</v>
+      </c>
+      <c r="H5" s="3">
+        <v>0.43459414324342821</v>
       </c>
       <c r="I5" s="3">
         <v>0.21452713874059057</v>
@@ -1044,14 +1041,10 @@
         <v/>
       </c>
       <c r="F6" t="s">
-        <v>90</v>
-      </c>
-      <c r="G6" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="H6" s="3" t="s">
-        <v>89</v>
-      </c>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
       <c r="I6" s="3">
         <v>0.59758823019714979</v>
       </c>
@@ -1079,11 +1072,11 @@
       <c r="F7" t="s">
         <v>6</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>89</v>
+      <c r="G7" s="3">
+        <v>0.30106784050434288</v>
+      </c>
+      <c r="H7" s="3">
+        <v>0.43326382946908459</v>
       </c>
       <c r="I7" s="3">
         <v>0.24865417698441153</v>
@@ -1147,18 +1140,18 @@
       <c r="C8" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="4" t="str">
+      <c r="D8" s="4">
         <f>IFERROR(VLOOKUP(B8,$F$3:$J$11,3,FALSE),"")</f>
-        <v>N/A</v>
+        <v>0.94168774792584609</v>
       </c>
       <c r="F8" t="s">
         <v>19</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>89</v>
+      <c r="G8" s="3">
+        <v>0.86193992895014826</v>
+      </c>
+      <c r="H8" s="3">
+        <v>0.94168774792584609</v>
       </c>
       <c r="I8" s="3">
         <v>0.89761085725848577</v>
@@ -1179,13 +1172,13 @@
         <f>-1/8.76</f>
         <v>-0.11415525114155252</v>
       </c>
-      <c r="Z8" s="2" t="str">
+      <c r="Z8" s="2">
         <f>VLOOKUP(V8,$F$3:$J$11,3,FALSE)</f>
-        <v>N/A</v>
-      </c>
-      <c r="AA8" s="2" t="e">
+        <v>0.68993375409691593</v>
+      </c>
+      <c r="AA8" s="2">
         <f>Z8*$AB$1</f>
-        <v>#VALUE!</v>
+        <v>0.75892712950660757</v>
       </c>
       <c r="AB8">
         <v>0</v>
@@ -1203,13 +1196,13 @@
         <f>-1/8.76</f>
         <v>-0.11415525114155252</v>
       </c>
-      <c r="AI8" s="2" t="str">
+      <c r="AI8" s="2">
         <f>VLOOKUP(AG8,$F$3:$J$11,2,FALSE)</f>
-        <v>N/A</v>
-      </c>
-      <c r="AJ8" t="e">
+        <v>0.37884710642106634</v>
+      </c>
+      <c r="AJ8">
         <f>AI8*$AD$1</f>
-        <v>#VALUE!</v>
+        <v>7.5769421284213267E-2</v>
       </c>
       <c r="AK8">
         <v>0</v>
@@ -1222,11 +1215,11 @@
       <c r="F9" t="s">
         <v>23</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>89</v>
+      <c r="G9" s="3">
+        <v>8.8500483037795494E-2</v>
+      </c>
+      <c r="H9" s="3">
+        <v>0.24242125602133488</v>
       </c>
       <c r="I9" s="3">
         <v>0.11213559179835184</v>
@@ -1247,13 +1240,13 @@
         <f>-1/8.76</f>
         <v>-0.11415525114155252</v>
       </c>
-      <c r="Z9" s="2" t="str">
+      <c r="Z9" s="2">
         <f>VLOOKUP(V9,$F$3:$J$11,3,FALSE)</f>
-        <v>N/A</v>
-      </c>
-      <c r="AA9" s="2" t="e">
+        <v>0.43459414324342821</v>
+      </c>
+      <c r="AA9" s="2">
         <f>Z9*$AB$1</f>
-        <v>#VALUE!</v>
+        <v>0.47805355756777107</v>
       </c>
       <c r="AB9">
         <v>0</v>
@@ -1271,13 +1264,13 @@
         <f>-1/8.76</f>
         <v>-0.11415525114155252</v>
       </c>
-      <c r="AI9" s="2" t="str">
+      <c r="AI9" s="2">
         <f>VLOOKUP(AG9,$F$3:$J$11,2,FALSE)</f>
-        <v>N/A</v>
-      </c>
-      <c r="AJ9" t="e">
+        <v>0.23254337785044626</v>
+      </c>
+      <c r="AJ9">
         <f>AI9*$AD$1</f>
-        <v>#VALUE!</v>
+        <v>4.6508675570089253E-2</v>
       </c>
       <c r="AK9">
         <v>0</v>
@@ -1290,11 +1283,11 @@
       <c r="F10" t="s">
         <v>9</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>89</v>
+      <c r="G10" s="3">
+        <v>3.6837332815181839E-2</v>
+      </c>
+      <c r="H10" s="3">
+        <v>0.20499200320398811</v>
       </c>
       <c r="I10" s="3">
         <v>0.12571540459727984</v>
@@ -1305,14 +1298,10 @@
     </row>
     <row r="11" spans="1:38" ht="14.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="F11" t="s">
-        <v>91</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>89</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
       <c r="I11" s="3">
         <v>0.39999922078326866</v>
       </c>
@@ -1322,13 +1311,13 @@
     </row>
     <row r="12" spans="1:38" x14ac:dyDescent="0.45">
       <c r="F12" t="s">
-        <v>92</v>
-      </c>
-      <c r="G12" t="s">
-        <v>89</v>
-      </c>
-      <c r="H12" t="s">
-        <v>89</v>
+        <v>91</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0.19932808100882485</v>
+      </c>
+      <c r="H12" s="3">
+        <v>0.34995147575899105</v>
       </c>
       <c r="I12" s="3">
         <v>0.20109032913765423</v>
@@ -1672,12 +1661,12 @@
   <sheetData>
     <row r="9" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C10" t="s">
         <v>69</v>
@@ -2027,7 +2016,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B10">
         <v>2000</v>
@@ -2153,7 +2142,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B19">
         <v>2001</v>
@@ -2279,7 +2268,7 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B28">
         <v>2002</v>
@@ -2405,7 +2394,7 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B37">
         <v>2003</v>
@@ -2531,7 +2520,7 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B46">
         <v>2004</v>
@@ -2657,7 +2646,7 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B55">
         <v>2005</v>
@@ -2783,7 +2772,7 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B64">
         <v>2006</v>
@@ -2909,7 +2898,7 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B73">
         <v>2007</v>
@@ -3035,7 +3024,7 @@
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B82">
         <v>2008</v>
@@ -3161,7 +3150,7 @@
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A91" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B91">
         <v>2009</v>
@@ -3287,7 +3276,7 @@
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A100" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B100">
         <v>2010</v>
@@ -3413,7 +3402,7 @@
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A109" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B109">
         <v>2011</v>
@@ -3539,7 +3528,7 @@
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A118" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B118">
         <v>2012</v>
@@ -3665,7 +3654,7 @@
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A127" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B127">
         <v>2013</v>
@@ -3791,7 +3780,7 @@
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A136" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B136">
         <v>2014</v>
@@ -3917,7 +3906,7 @@
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A145" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B145">
         <v>2015</v>
@@ -4043,7 +4032,7 @@
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A154" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B154">
         <v>2016</v>
@@ -4169,7 +4158,7 @@
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A163" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B163">
         <v>2017</v>
@@ -4295,7 +4284,7 @@
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A172" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B172">
         <v>2018</v>
@@ -4421,7 +4410,7 @@
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A181" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B181">
         <v>2019</v>
@@ -4547,7 +4536,7 @@
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A190" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B190">
         <v>2020</v>
@@ -4673,7 +4662,7 @@
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A199" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B199">
         <v>2021</v>
@@ -4799,7 +4788,7 @@
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A208" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B208">
         <v>2022</v>
@@ -4925,7 +4914,7 @@
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A217" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B217">
         <v>2023</v>
@@ -5051,7 +5040,7 @@
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A226" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B226">
         <v>2000</v>
@@ -5177,7 +5166,7 @@
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A235" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B235">
         <v>2001</v>
@@ -5303,7 +5292,7 @@
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A244" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B244">
         <v>2002</v>
@@ -5429,7 +5418,7 @@
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A253" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B253">
         <v>2003</v>
@@ -5555,7 +5544,7 @@
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A262" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B262">
         <v>2004</v>
@@ -5681,7 +5670,7 @@
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A271" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B271">
         <v>2005</v>
@@ -5807,7 +5796,7 @@
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A280" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B280">
         <v>2006</v>
@@ -5933,7 +5922,7 @@
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A289" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B289">
         <v>2007</v>
@@ -6059,7 +6048,7 @@
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A298" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B298">
         <v>2008</v>
@@ -6185,7 +6174,7 @@
     </row>
     <row r="307" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A307" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B307">
         <v>2009</v>
@@ -6311,7 +6300,7 @@
     </row>
     <row r="316" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A316" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B316">
         <v>2010</v>
@@ -6437,7 +6426,7 @@
     </row>
     <row r="325" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A325" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B325">
         <v>2011</v>
@@ -6563,7 +6552,7 @@
     </row>
     <row r="334" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A334" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B334">
         <v>2012</v>
@@ -6689,7 +6678,7 @@
     </row>
     <row r="343" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A343" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B343">
         <v>2013</v>
@@ -6815,7 +6804,7 @@
     </row>
     <row r="352" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A352" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B352">
         <v>2014</v>
@@ -6941,7 +6930,7 @@
     </row>
     <row r="361" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A361" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B361">
         <v>2015</v>
@@ -7067,7 +7056,7 @@
     </row>
     <row r="370" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A370" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B370">
         <v>2016</v>
@@ -7193,7 +7182,7 @@
     </row>
     <row r="379" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A379" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B379">
         <v>2017</v>
@@ -7319,7 +7308,7 @@
     </row>
     <row r="388" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A388" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B388">
         <v>2018</v>
@@ -7445,7 +7434,7 @@
     </row>
     <row r="397" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A397" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B397">
         <v>2019</v>
@@ -7571,7 +7560,7 @@
     </row>
     <row r="406" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A406" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B406">
         <v>2020</v>
@@ -7697,7 +7686,7 @@
     </row>
     <row r="415" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A415" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B415">
         <v>2021</v>
@@ -7823,7 +7812,7 @@
     </row>
     <row r="424" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A424" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B424">
         <v>2022</v>
@@ -7949,7 +7938,7 @@
     </row>
     <row r="433" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A433" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B433">
         <v>2023</v>
@@ -8075,7 +8064,7 @@
     </row>
     <row r="442" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A442" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B442">
         <v>2000</v>
@@ -8201,7 +8190,7 @@
     </row>
     <row r="451" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A451" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B451">
         <v>2001</v>
@@ -8327,7 +8316,7 @@
     </row>
     <row r="460" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A460" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B460">
         <v>2002</v>
@@ -8453,7 +8442,7 @@
     </row>
     <row r="469" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A469" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B469">
         <v>2003</v>
@@ -8579,7 +8568,7 @@
     </row>
     <row r="478" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A478" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B478">
         <v>2004</v>
@@ -8705,7 +8694,7 @@
     </row>
     <row r="487" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A487" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B487">
         <v>2005</v>
@@ -8831,7 +8820,7 @@
     </row>
     <row r="496" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A496" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B496">
         <v>2006</v>
@@ -8957,7 +8946,7 @@
     </row>
     <row r="505" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A505" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B505">
         <v>2007</v>
@@ -9083,7 +9072,7 @@
     </row>
     <row r="514" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A514" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B514">
         <v>2008</v>
@@ -9209,7 +9198,7 @@
     </row>
     <row r="523" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A523" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B523">
         <v>2009</v>
@@ -9335,7 +9324,7 @@
     </row>
     <row r="532" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A532" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B532">
         <v>2010</v>
@@ -9461,7 +9450,7 @@
     </row>
     <row r="541" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A541" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B541">
         <v>2011</v>
@@ -9587,7 +9576,7 @@
     </row>
     <row r="550" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A550" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B550">
         <v>2012</v>
@@ -9713,7 +9702,7 @@
     </row>
     <row r="559" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A559" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B559">
         <v>2013</v>
@@ -9839,7 +9828,7 @@
     </row>
     <row r="568" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A568" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B568">
         <v>2014</v>
@@ -9965,7 +9954,7 @@
     </row>
     <row r="577" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A577" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B577">
         <v>2015</v>
@@ -10091,7 +10080,7 @@
     </row>
     <row r="586" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A586" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B586">
         <v>2016</v>
@@ -10217,7 +10206,7 @@
     </row>
     <row r="595" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A595" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B595">
         <v>2017</v>
@@ -10343,7 +10332,7 @@
     </row>
     <row r="604" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A604" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B604">
         <v>2018</v>
@@ -10469,7 +10458,7 @@
     </row>
     <row r="613" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A613" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B613">
         <v>2019</v>
@@ -10595,7 +10584,7 @@
     </row>
     <row r="622" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A622" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B622">
         <v>2020</v>
@@ -10721,7 +10710,7 @@
     </row>
     <row r="631" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A631" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B631">
         <v>2021</v>
@@ -10847,7 +10836,7 @@
     </row>
     <row r="640" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A640" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B640">
         <v>2022</v>
@@ -10973,7 +10962,7 @@
     </row>
     <row r="649" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A649" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B649">
         <v>2023</v>

--- a/VerveStacks_USA/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_USA/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_USA\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9D3E65E1-4A1A-4410-99D2-42D8698516C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2EBFBACF-F915-4448-9306-288BE1A54EA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_USA/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_USA/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_USA\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2EBFBACF-F915-4448-9306-288BE1A54EA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{07B4865C-7072-4706-A7B7-781B985135F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_USA/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_USA/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_USA\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{07B4865C-7072-4706-A7B7-781B985135F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0944C140-5C4E-4050-9D6F-4D4CBC7E386B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_USA/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_USA/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_USA\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0944C140-5C4E-4050-9D6F-4D4CBC7E386B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F4DAD716-8F59-49C8-A670-E7B535FE98B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_USA/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_USA/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_USA\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F4DAD716-8F59-49C8-A670-E7B535FE98B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EEA9693E-0363-40C2-9A8D-BC2814CE86A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_USA/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_USA/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_USA\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EEA9693E-0363-40C2-9A8D-BC2814CE86A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1597CD28-B025-4367-AD64-697430C6A705}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_USA/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_USA/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_USA\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1597CD28-B025-4367-AD64-697430C6A705}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2431941B-3DB2-4985-87FA-11EF3C86C0D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_USA/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_USA/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_USA\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2431941B-3DB2-4985-87FA-11EF3C86C0D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3567EC0A-802C-485D-AF47-E2C5D67C3463}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_USA/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_USA/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_USA\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{77C9554B-6E51-4B98-AF8B-C566AD22ABDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DC9DA6C9-D404-4B34-9794-F2A58F4C115F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1008,7 +1008,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A434D16-A1B5-4CF0-AD89-BB0EC8069CEE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F36F9271-70DF-4DDC-8297-962A60C5AF59}">
   <dimension ref="B9:L56"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
